--- a/data/trans_orig/IP3109_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Provincia-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>43908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>96016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89767</t>
+          <t>90115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99261</t>
+          <t>99305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190880</t>
+          <t>191335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107693</t>
+          <t>107701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116984</t>
+          <t>117501</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121159</t>
+          <t>120517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241276</t>
+          <t>241324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>246317</t>
+          <t>246316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139623</t>
+          <t>139546</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147067</t>
+          <t>146902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288719</t>
+          <t>288612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294232</t>
+          <t>294270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>621017</t>
+          <t>621727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>628319</t>
+          <t>628439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>664625</t>
+          <t>665100</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>670309</t>
+          <t>670356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,42 +3527,42 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1294077</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>1288427</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>1297908</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>98,97%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1294077</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>1289399</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>1297914</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,47 +3640,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3947</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>13428</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51898</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56692</t>
+          <t>56220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104897</t>
+          <t>104531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112018</t>
+          <t>111986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89353</t>
+          <t>89270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94010</t>
+          <t>94009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92174</t>
+          <t>91912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>183919</t>
+          <t>183854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189224</t>
+          <t>189220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>58188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122563</t>
+          <t>121975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66336</t>
+          <t>67416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146905</t>
+          <t>146209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44124</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46094</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100195</t>
+          <t>100196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124698</t>
+          <t>124727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244760</t>
+          <t>244754</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148797</t>
+          <t>148732</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154760</t>
+          <t>155189</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>306487</t>
+          <t>306229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>311777</t>
+          <t>311778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>630524</t>
+          <t>630783</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>640821</t>
+          <t>641741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>672531</t>
+          <t>673390</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>681309</t>
+          <t>681379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1307020</t>
+          <t>1307067</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1320376</t>
+          <t>1320709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46648</t>
+          <t>46601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>57217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106218</t>
+          <t>106661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113204</t>
+          <t>113215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116932</t>
+          <t>117526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67157</t>
+          <t>67205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142793</t>
+          <t>143135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47386</t>
+          <t>47938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102399</t>
+          <t>102387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>116802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123907</t>
+          <t>123234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242785</t>
+          <t>242735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247328</t>
+          <t>247325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146075</t>
+          <t>145807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>299719</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>623967</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>633248</t>
+          <t>633158</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>671670</t>
+          <t>671595</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>678192</t>
+          <t>678189</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1298837</t>
+          <t>1298866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1310327</t>
+          <t>1310047</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58179</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67254</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>64575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112241</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129680</t>
+          <t>129223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98102</t>
+          <t>97428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116637</t>
+          <t>117012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103534</t>
+          <t>102972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>117048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207326</t>
+          <t>207057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229934</t>
+          <t>229189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27547</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>22882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>48917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51499</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82333</t>
+          <t>82968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97445</t>
+          <t>97395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>37217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58058</t>
+          <t>58128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66498</t>
+          <t>66562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73350</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126181</t>
+          <t>126205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138272</t>
+          <t>138447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>60639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69525</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61068</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22893</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98075</t>
+          <t>97582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111344</t>
+          <t>111251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126363</t>
+          <t>126336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141616</t>
+          <t>141637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228344</t>
+          <t>228722</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248787</t>
+          <t>250626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50396</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118153</t>
+          <t>117144</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126073</t>
+          <t>125581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142568</t>
+          <t>142974</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151544</t>
+          <t>151516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263807</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275850</t>
+          <t>275697</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>546448</t>
+          <t>546713</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>578200</t>
+          <t>578076</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>610647</t>
+          <t>612287</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>648538</t>
+          <t>648671</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1167812</t>
+          <t>1170793</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1216947</t>
+          <t>1216566</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>74233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105861</t>
+          <t>105596</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>95631</t>
+          <t>95498</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>131882</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179531</t>
+          <t>179912</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>228666</t>
+          <t>225685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
